--- a/Test Files/Steerable Intake Scenarios.xlsx
+++ b/Test Files/Steerable Intake Scenarios.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cold Brew Co (1-LOB Product)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVAC (2-LOB Service)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vet Clinic (3-LOB Consumer)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plumbing-HVAC Startup (2-LOB)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Composting Co (3-LOB)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Software Co (3-LOB Enterprise)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4175,4 +4178,3928 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Your input</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>What this controls / options (documentation only - the runner ignores this column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Test a pre-launch home-services startup: a new plumbing company that specializes in HVAC systems, run by two founders out of a home garage with one work truck. The start date is in the near future, so this is a pre-launch business - the numbers are Year-1 projections, not history. Two lines of revenue with different economics. The founders are optimistic but green, hedge on their ramp-up utilization, and answer a couple of things at once. This test exercises pre-launch treatment, a lean startup balance sheet, no lease and no debt (equity-only), and a business that hasn't opened yet.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED. The business story + what this test is about. Sets the client's persona and tone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Business name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TrueLine Plumbing &amp; HVAC</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Exact business name the client gives. Leave blank to let the client-GPT invent one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Business address</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1420 Vandalia St, St Paul, MN 55114, USA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Full US address (street, city, state, ZIP, country) - the form needs all parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Business start date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>08/19/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY. Determines operating vs pre-launch treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CONTROLLED ANSWERS &amp; BEHAVIORS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>One position per row. Column A = optional topic label (any text). Column B = the position/answer/behavior - values AND behaviors both work. Add/delete rows freely; divider rows with empty column B are ignored by the runner.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: structure -</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Service line structure</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Two separate lines of business with different economics: (1) HVAC System Installation - installing and replacing heating and cooling systems, and (2) Plumbing Service &amp; Repair - service calls and repairs. Track them separately.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>THE LOB COUNT LIVES HERE + one economics block per line below. For ONE line write e.g. 'One core service line only: Physical Therapy' (see the Single LOB sheet). For 2, 3, or more: name each line here and add/delete the matching economics blocks. NOTE: the app may still model them as one LOB with N products - per-line economics stay separate either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Customer type</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>mixed - mostly residential homeowners, with some small-commercial service work.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>consumer / b2b / mixed. Drives which Target Market questions appear (B2B rows below only fire if businesses are mentioned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Legal entity</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The business is an LLC.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Options the app accepts: Sole proprietor, LLC, LLP, S-corp, C-corp, Partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: per-line economics (repeat this block per line) -</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HVAC Installation - unit definition</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>For HVAC Installation, one unit is one completed system installation job.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HVAC Installation - cadence</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Monthly - capacity is how many installs we can complete per month.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HVAC Installation - capacity</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Starting out, with one crew we can do about 10 installs a month.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HVAC Installation - utilization</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>We're brand new, so use 40% utilization for Year 1 - if the consultant proposes a higher percentage, decline and insist on 40% while we ramp up.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HVAC Installation - price</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>The average installation runs about $7,500.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Plumbing Service &amp; Repair - unit definition</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>For Plumbing Service &amp; Repair, one unit is one service or repair call.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Plumbing Service &amp; Repair - cadence</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Weekly - capacity is calls per week.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Plumbing Service &amp; Repair - capacity</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>We can handle about 30 service calls a week once both founders are running.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Plumbing Service &amp; Repair - utilization</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Use 45% utilization for Year 1 on service calls - insist on 45% if a different number is proposed, since we're just getting started.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Plumbing Service &amp; Repair - price</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>The average service call runs about $300.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Turnover / turns per year</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Install jobs are one-and-done; service calls turn over weekly. No long-term contracts.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>For contract-style businesses say 'each slot turns over about N times per year' - it becomes operating periods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: business-wide -</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Delivery method</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>In person - all work is done at the customer's home or building.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>How clients receive the product/service (in person / online / shipped / hybrid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sales channel</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Google Local Services ads, a few home-service marketplace listings, and word of mouth from the founders' networks.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>How business comes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>The Minneapolis-St. Paul metro - local only to start.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Local / regional / national scope + coverage area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Growth lever</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Growth comes from adding a second crew and a service tech so we can take more jobs.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>The primary growth driver the plan should assume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Competitive advantage</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Two licensed founders who do the work themselves - fast, honest, licensed plumbing plus HVAC under one roof, so customers don't need two contractors.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>The differentiation story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>12-month goal</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Reach about $60,000 in monthly revenue within 12 months.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Becomes a concrete milestone with timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Concrete milestones: pass licensing and open for jobs by month 1; hire a first service technician by month 6.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Give CONCRETE milestones with timing. (A bare count like 'track five milestones' has no field in SQL - only concrete milestones persist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Confidence in these projections is 5 out of 10 - we're a brand-new startup.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>The ops confidence rating (X out of 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>- TARGET MARKET -</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Gender focus</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>No gender focus - all genders.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>all / men / women.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Age range</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Homeowners roughly 30 to 70.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Formats that parse: '30 to 65', '45+', '18 and up', 'no age preference'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Household income 70k and up.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Formats: '60k to 120k', '75k and up', 'under 100k'. Shorthand (k/m) is understood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>No education preference.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>A specific level, or no preference (lands only in the late demographics batch, not as its own field).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Demographic segments</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Include household structure and housing economics - we care about homeowners; keep the rest broad.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Which optional segments to include: household structure, employment, housing economics - or skip. NOTE: these land in SQL as one batch at the end of the market section, not per answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Employment specifics</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Working homeowners and retirees who own their homes.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>The choices inside an included segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>B2B industries</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>For the small-commercial work, target small businesses and property managers with a handful of units.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Only asked if customer type mentions businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>B2B size / age</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Small commercial sites of roughly 5 to 50 employees; age doesn't matter.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Employee-count band and firm-age band for B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Positioning summary</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>When the market summary is presented, accept it as-is.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: accept as-is, or request a specific refinement before confirming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>- PEOPLE / HR -</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Key person 1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Marcus Reilly, Co-Founder and Master Plumber, 12 years in the trade, master plumbing license, plans to draw about $60,000 in Year 1.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Full detail: name, title, years, background, wage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Key person 2</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Kyle Barrett, Co-Founder and HVAC Lead, 9 years in HVAC, EPA-certified - let the consultant estimate his draw.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Wage can be omitted - the app estimates it (wage_source shows it was estimated, not client-set).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Done adding people</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>After the two founders, say the key people list is complete.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>When to stop - triggers the people wrap-up (paragraphs + suggested future roles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Suggested roles - wage</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>If a service technician or apprentice role is suggested, set its wage to $46,000.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: override a suggested role's estimated wage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Suggested roles - timing</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Any suggested additional hire should be planned for about 6 months out.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: set months-until-hire on a suggested role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: baselines (accept / adjust behaviors) -</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Revenue baseline</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Accept the Year-1 revenue projection as presented.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Or: adjust a driver ('actually make PT utilization 75%'), or pick a presented option by number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>COGS runs about 45% of revenue - equipment, parts, and materials.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Options: accept baseline / set a dollar amount / set a percent of revenue / 'use 0 for COGS'. Accept-then-adjust exercises the correction path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Accept the Year-1 payroll baseline as presented.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Accept, or push to an exact number. Baseline derives from the People section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>We plan to spend about 1.5k a month on marketing.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phrasing tests the monthly-to-annual conversion (3k/mo should land as 36,000/yr). Or give an annual total or a percent of revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: the scalar questions (one each) -</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Monthly rent</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>We work out of a home garage - no shop rent.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Or 'we work from home' - lands as 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Future rent expected</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Not for now - we'll run from the garage until we outgrow it, then revisit.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no boolean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Owner compensation</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>We haven't paid ourselves yet; once we open we each plan to draw about $5,000 a month.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phrasing tests the x12 annualization (should land ~108,000). Or state an annual figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Other operating expense</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Other monthly costs - fuel, insurance, licensing, software - run about $2,200.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Utilities, software, insurance, etc. - monthly figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Employee count</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Just the 2 founders on payroll at launch.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Whole number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>We're spending about $45,000 to launch - a used work truck plus tools and equipment.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Larger one-time purchases; 'none' lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Initial assets</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>The truck, tools, and equipment are worth about $45,000.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Total value of existing equipment/fixtures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Initial lease</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>No leases - none.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Monthly lease beyond main rent; 'none' lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Initial equity</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>The two founders are putting in about $80,000 of their own money.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Owner/investor money invested to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>No debt - we're funding it ourselves, we don't owe anything.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANT: a value of 0 auto-fills the next three debt answers as 0 and skips those questions. Non-zero makes them all fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Other monthly debt payments</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - no debt, so this auto-fills to $0 and isn't asked.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Annual interest</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - no debt (auto-filled to $0).</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Annual principal</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - no debt (auto-filled to $0).</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>About 40k in the bank to start.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Business cash balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>None yet - we haven't started billing customers.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Shorthand like '40k' is understood (lands 40,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Just a little - about $3,000 in pre-opening bills.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Unpaid supplier invoices, utilities, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>A small starting stock of parts - about $6,000.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>'None/zero' phrasing lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: strategy + funding (end of intake) -</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Cash strategy</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Preserve cash - we're keeping every dollar in the business while we get off the ground.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Options: preserve cash / shareholder return / balanced. Answering vaguely on purpose tests the app's clarify-then-forced-choice ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Funding preference</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Fund it with equity only - our own money and maybe a friends-and-family investor; no loans.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>debt / equity / both. Choosing debt-only or equity-only SKIPS the split question; 'both' triggers it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Funding split</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - equity-only funding, so no split question is asked.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Only asked after 'both'. Words work ('seventy percent debt'); lands as 0.7 / 0.5 / 0.3 debt share - off-menu answers snap to the nearest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>- CROSS-CUTTING CONVERSATION BEHAVIORS -</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Messy-English style</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Give some of the financial answers in casual shorthand - things like '40k' or '1.5k a month' instead of formal figures.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Exercises the NL-understanding layer's normalization on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Compound answer</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>When asked about delivery, answer that and also volunteer the sales channel in the same reply.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Tests multi-fact extraction from one message.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Your input</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>What this controls / options (documentation only - the runner ignores this column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Test a young but operating circular-economy business: a commercial and residential composting company that collects food and organic waste and turns it into finished compost. It has been operating for only a few weeks, so Year-1 figures are early and ramping. Three separate lines tracked with different economics - residential pickup subscriptions, commercial hauling contracts, and finished-compost product sales. The owner is mission-driven and detail-oriented, holds firm on early utilization, nudges one cost baseline up, and sometimes bundles two facts into one answer. This test exercises three mixed lines (two service, one product), a leased equipment asset, moderate equipment debt, and 50/50 debt-and-equity funding.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED. The business story + what this test is about. Sets the client's persona and tone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Business name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Rootcycle Compost Co.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Exact business name the client gives. Leave blank to let the client-GPT invent one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Business address</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3900 Bandini Blvd, Vernon, CA 90058, USA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Full US address (street, city, state, ZIP, country) - the form needs all parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Business start date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY. Determines operating vs pre-launch treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CONTROLLED ANSWERS &amp; BEHAVIORS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>One position per row. Column A = optional topic label (any text). Column B = the position/answer/behavior - values AND behaviors both work. Add/delete rows freely; divider rows with empty column B are ignored by the runner.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: structure -</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Service line structure</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Three separate lines of business with different economics: (1) Residential Compost Pickup subscriptions, (2) Commercial Organic-Waste Hauling contracts, and (3) Finished Compost &amp; Soil product sales. Insist they are tracked separately.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>THE LOB COUNT LIVES HERE + one economics block per line below. For ONE line write e.g. 'One core service line only: Physical Therapy' (see the Single LOB sheet). For 2, 3, or more: name each line here and add/delete the matching economics blocks. NOTE: the app may still model them as one LOB with N products - per-line economics stay separate either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Customer type</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>mixed - residential subscribers and consumers on the product side, plus commercial hauling accounts.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>consumer / b2b / mixed. Drives which Target Market questions appear (B2B rows below only fire if businesses are mentioned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Legal entity</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The business is an S-corp.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Options the app accepts: Sole proprietor, LLC, LLP, S-corp, C-corp, Partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: per-line economics (repeat this block per line) -</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Residential Pickup - unit definition</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>For Residential Pickup, one unit is one active monthly residential subscription.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Residential Pickup - cadence</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Monthly - capacity is how many subscribers we can service per month.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Residential Pickup - capacity</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Our routes can support up to about 2,500 residential subscribers.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Residential Pickup - utilization</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>We just launched, so use 40% utilization for Year 1 - if the consultant proposes a higher percentage, decline and insist on 40%.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Residential Pickup - price</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Residential subscriptions average about $32 a month.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Hauling - unit definition</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>For Commercial Hauling, one unit is one active commercial hauling contract.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Hauling - cadence</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Contract - monthly billing on ongoing accounts; capacity is how many accounts we can carry.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Hauling - capacity</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>We can carry up to about 120 active commercial accounts.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Hauling - utilization</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Use 45% utilization on commercial accounts for Year 1 - insist on 45% if a different number is proposed.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Hauling - price</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Commercial hauling contracts average about $650 a month per account.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Finished Compost - unit definition</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>For Finished Compost, one unit is one cubic yard of finished compost sold, bulk or bagged.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Finished Compost - cadence</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Monthly - capacity is cubic yards we can process and sell per month.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Finished Compost - capacity</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>At full processing we can move about 1,800 cubic yards a month.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Finished Compost - utilization</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Use 35% utilization for Year 1 on product sales - insist on 35% while the product side ramps.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Finished Compost - price</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Finished compost averages about $38 a cubic yard.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Turnover / turns per year</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Subscriptions and commercial accounts renew monthly; finished compost is produced and sold each month - inventory turns over monthly.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>For contract-style businesses say 'each slot turns over about N times per year' - it becomes operating periods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: business-wide -</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Delivery method</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid - we pick up waste on scheduled routes with our trucks, and we deliver or let customers pick up finished compost at the yard.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>How clients receive the product/service (in person / online / shipped / hybrid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Sales channel</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Direct residential sign-ups online, an outreach team for restaurants and grocers, and a couple of landscape-supply resellers for the finished product.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>How business comes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Regional - the greater Los Angeles area for now, with room to add routes.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Local / regional / national scope + coverage area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Growth lever</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Growth comes from adding collection routes and signing more commercial accounts to feed the processing yard.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>The primary growth driver the plan should assume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Competitive advantage</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A closed-loop story customers can see - local pickup that comes back as local compost - plus commercial diversion reporting that helps businesses hit waste-diversion mandates.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>The differentiation story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>12-month goal</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Reach about $110,000 in monthly revenue within 12 months.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Becomes a concrete milestone with timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Concrete milestones: reach 1,000 residential subscribers by month 6; sell out the first full batch of finished compost by month 9.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Give CONCRETE milestones with timing. (A bare count like 'track five milestones' has no field in SQL - only concrete milestones persist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Confidence in these numbers is 6 out of 10 - we're only a few weeks in.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>The ops confidence rating (X out of 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>- TARGET MARKET -</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Gender focus</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>No gender focus - all genders.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>all / men / women.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Age range</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Residential customers roughly 28 to 60.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Formats that parse: '30 to 65', '45+', '18 and up', 'no age preference'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Household income 70k and up - sustainability-minded households.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Formats: '60k to 120k', '75k and up', 'under 100k'. Shorthand (k/m) is understood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Skews college-educated, but no hard preference.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>A specific level, or no preference (lands only in the late demographics batch, not as its own field).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Demographic segments</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Include household structure, employment, and housing economics.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Which optional segments to include: household structure, employment, housing economics - or skip. NOTE: these land in SQL as one batch at the end of the market section, not per answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Employment specifics</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Environmentally-conscious professionals and homeowners.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>The choices inside an included segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>B2B industries</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>For commercial accounts, target restaurants, grocery stores, corporate cafeterias, and landscapers.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Only asked if customer type mentions businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>B2B size / age</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Food-service and grocery sites of roughly 20 to 300 employees; established businesses under waste-diversion rules.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Employee-count band and firm-age band for B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Positioning summary</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>When the market summary is presented, ask for one change - emphasize the commercial waste-diversion compliance angle - then approve.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: accept as-is, or request a specific refinement before confirming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>- PEOPLE / HR -</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Key person 1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Nadia Okonkwo, Founder and CEO, 10 years in waste and sustainability operations, environmental-science background, earns $95,000 a year.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Full detail: name, title, years, background, wage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Key person 2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Ruiz, Operations and Yard Manager, 14 years in hauling and heavy equipment - let the consultant estimate his compensation.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Wage can be omitted - the app estimates it (wage_source shows it was estimated, not client-set).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Done adding people</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>After those two, say the key people list is complete.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>When to stop - triggers the people wrap-up (paragraphs + suggested future roles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Suggested roles - wage</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>If a route-driver or sales role is suggested, set its wage to $50,000.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: override a suggested role's estimated wage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Suggested roles - timing</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Any suggested additional driver should be planned for about 4 months out.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: set months-until-hire on a suggested role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: baselines (accept / adjust behaviors) -</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Revenue baseline</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Accept the Year-1 revenue baseline as presented.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Or: adjust a driver ('actually make PT utilization 75%'), or pick a presented option by number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>When the COGS/direct-cost baseline is proposed, first accept it, then adjust it up to $360,000 and confirm the restated number - fuel and processing cost us more than a typical baseline assumes.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Options: accept baseline / set a dollar amount / set a percent of revenue / 'use 0 for COGS'. Accept-then-adjust exercises the correction path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Accept the Year-1 payroll baseline as presented.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Accept, or push to an exact number. Baseline derives from the People section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>We spend about $4,000 a month on marketing and outreach.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phrasing tests the monthly-to-annual conversion (3k/mo should land as 36,000/yr). Or give an annual total or a percent of revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: the scalar questions (one each) -</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Monthly rent</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Rent on the processing yard and site is $5,500 a month.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Or 'we work from home' - lands as 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Future rent expected</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Yes - we'll always need the processing yard.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no boolean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Owner compensation</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Last month I paid myself $7,000.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phrasing tests the x12 annualization (should land ~108,000). Or state an annual figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Other operating expense</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Other monthly costs - fuel, insurance, permits, dumping fees, software - run about $8,500.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Utilities, software, insurance, etc. - monthly figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Employee count</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>We have 10 people on payroll.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Whole number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>We spent about $150,000 recently on two collection trucks and a compost screener.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Larger one-time purchases; 'none' lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Initial assets</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>The trucks, screener, and yard equipment are worth about $260,000.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Total value of existing equipment/fixtures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Initial lease</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>We lease a wheel loader for the yard at $2,400 a month beyond the rent.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Monthly lease beyond main rent; 'none' lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Initial equity</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>About $250,000 of equity has gone into the business so far.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Owner/investor money invested to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>We owe about $280,000 on equipment financing.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANT: a value of 0 auto-fills the next three debt answers as 0 and skips those questions. Non-zero makes them all fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Other monthly debt payments</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>The equipment loan payments run about $4,200 a month.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Annual interest</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Annual interest is about $14,000.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Annual principal</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>We pay down about $40,000 of principal a year.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>About $70,000 in the bank.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Business cash balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Commercial accounts owe us about $45,000 on net-30 terms.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Shorthand like '40k' is understood (lands 40,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>We owe about $30,000 to fuel, equipment, and disposal vendors.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Unpaid supplier invoices, utilities, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>We carry about $35,000 in finished compost and bagged product.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>'None/zero' phrasing lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: strategy + funding (end of intake) -</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Cash strategy</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Balanced - keep a cushion, pay down the equipment loan responsibly, and reinvest the rest into routes.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Options: preserve cash / shareholder return / balanced. Answering vaguely on purpose tests the app's clarify-then-forced-choice ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Funding preference</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Fund it with a mix of both debt and equity.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>debt / equity / both. Choosing debt-only or equity-only SKIPS the split question; 'both' triggers it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Funding split</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Roughly fifty percent debt and fifty percent equity - a 50/50 split.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Only asked after 'both'. Words work ('seventy percent debt'); lands as 0.7 / 0.5 / 0.3 debt share - off-menu answers snap to the nearest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>- CROSS-CUTTING CONVERSATION BEHAVIORS -</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Compound answer</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>When asked about delivery, answer that and also volunteer the sales channel in the same reply.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Tests multi-fact extraction from one message.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Your input</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>What this controls / options (documentation only - the runner ignores this column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Test a large, established B2B software company. It has been operating for several years and runs at scale - tens of millions in revenue and hundreds of employees. Three separate lines tracked with different economics - self-serve SaaS subscriptions, enterprise annual contracts, and professional services. The finance lead is precise, sets exact figures rather than accepting rough baselines, asks the consultant to clarify definitions, and expects the plan to reflect enterprise SaaS economics. This test exercises large-dollar figures, a B2B/enterprise market, a real office and equipment lease, venture-debt-plus-equity funding, and a zero-inventory software business.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED. The business story + what this test is about. Sets the client's persona and tone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Business name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Northwind Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Exact business name the client gives. Leave blank to let the client-GPT invent one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Business address</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>500 108th Ave NE, Bellevue, WA 98004, USA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Full US address (street, city, state, ZIP, country) - the form needs all parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Business start date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2021</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY. Determines operating vs pre-launch treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CONTROLLED ANSWERS &amp; BEHAVIORS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>One position per row. Column A = optional topic label (any text). Column B = the position/answer/behavior - values AND behaviors both work. Add/delete rows freely; divider rows with empty column B are ignored by the runner.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: structure -</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Service line structure</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Three separate lines of business with different economics: (1) Self-Serve SaaS Subscriptions, (2) Enterprise Annual Contracts, and (3) Professional Services &amp; Implementation. Insist they are tracked separately.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>THE LOB COUNT LIVES HERE + one economics block per line below. For ONE line write e.g. 'One core service line only: Physical Therapy' (see the Single LOB sheet). For 2, 3, or more: name each line here and add/delete the matching economics blocks. NOTE: the app may still model them as one LOB with N products - per-line economics stay separate either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Customer type</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>b2b - we sell to businesses, from small self-serve customers up to large enterprises.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>consumer / b2b / mixed. Drives which Target Market questions appear (B2B rows below only fire if businesses are mentioned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Legal entity</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The business is a C-corp.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Options the app accepts: Sole proprietor, LLC, LLP, S-corp, C-corp, Partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: per-line economics (repeat this block per line) -</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SaaS Subscriptions - unit definition</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>For SaaS Subscriptions, one unit is one active monthly subscription account.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SaaS Subscriptions - cadence</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Monthly - capacity is active subscriptions we can serve per month.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SaaS Subscriptions - capacity</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>The platform can support up to about 60,000 active subscription accounts.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SaaS Subscriptions - utilization</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Use 70% utilization for Year 1 - if the consultant proposes a different percentage, decline and insist on 70%.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SaaS Subscriptions - price</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Subscriptions average about $85 per account per month.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Contracts - unit definition</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>For Enterprise Contracts, one unit is one active enterprise annual contract.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Contracts - cadence</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Contract - annual contracts; capacity is how many enterprise accounts we can carry at once.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Contracts - capacity</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>We can carry up to about 900 concurrent enterprise contracts.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Contracts - utilization</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Use 65% utilization on enterprise for Year 1 - insist on 65% if a different number is proposed.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Contracts - price</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise contracts average about $95,000 a year each.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Professional Services - unit definition</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>For Professional Services, one unit is one implementation or services engagement.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>What counts as one unit for the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Professional Services - cadence</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Monthly - capacity is engagements our services team can deliver per month.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>weekly / monthly / contract. Controls whether capacity is asked per week or per period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Professional Services - capacity</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>The services team can deliver about 100 engagements a month.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>The max-capacity number. Phrase per week or per month to match the cadence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Professional Services - utilization</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Use 60% utilization on services for Year 1 - insist on 60% if a different number is proposed.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Utilization % + an insist-behavior. The decline-and-insist wording is what beats the consultant's default 70-80% proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Professional Services - price</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Services engagements average about $22,000 each.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Unit price / average fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Turnover / turns per year</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Subscriptions renew monthly; enterprise contracts renew annually; services engagements turn over as they're delivered.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>For contract-style businesses say 'each slot turns over about N times per year' - it becomes operating periods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>- OPERATIONS: business-wide -</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Delivery method</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Online - the product is cloud-based SaaS delivered over the web, with remote implementation and support.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>How clients receive the product/service (in person / online / shipped / hybrid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Sales channel</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>An enterprise sales team for large accounts, self-serve online signup for smaller customers, and a partner and reseller channel.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>How business comes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>National and international - we sell across North America and Europe.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Local / regional / national scope + coverage area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Growth lever</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Growth comes from landing and expanding enterprise accounts and moving up-market to larger customers.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>The primary growth driver the plan should assume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Competitive advantage</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Deep product integrations and a platform ecosystem that raise switching costs, plus enterprise-grade security and compliance that win large deals.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>The differentiation story.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>12-month goal</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Reach about $12 million in monthly revenue within 12 months.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Becomes a concrete milestone with timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Concrete milestones: close our first eight-figure enterprise contract by month 6; launch the public platform API and partner marketplace by month 9.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Give CONCRETE milestones with timing. (A bare count like 'track five milestones' has no field in SQL - only concrete milestones persist.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Confidence in these numbers is 8 out of 10.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>The ops confidence rating (X out of 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>- TARGET MARKET -</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Gender focus</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>No gender focus - all genders; our buyers are businesses.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>all / men / women.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Age range</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Decision-makers are roughly 30 to 55 - but no strict age preference.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Formats that parse: '30 to 65', '45+', '18 and up', 'no age preference'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Not really applicable - we sell to businesses, not consumers.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Formats: '60k to 120k', '75k and up', 'under 100k'. Shorthand (k/m) is understood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>No education preference.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>A specific level, or no preference (lands only in the late demographics batch, not as its own field).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Demographic segments</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Keep the consumer demographic segments broad - the meaningful targeting is the B2B firmographics below.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Which optional segments to include: household structure, employment, housing economics - or skip. NOTE: these land in SQL as one batch at the end of the market section, not per answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Employment specifics</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable at the consumer level - our targeting is firmographic.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>The choices inside an included segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>B2B industries</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Target mid-market and enterprise companies in technology, financial services, healthcare, and retail.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Only asked if customer type mentions businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>B2B size / age</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Companies from about 200 to 5,000-plus employees; established organizations.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Employee-count band and firm-age band for B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Positioning summary</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>When the market summary is presented, ask for one change - emphasize the enterprise security and compliance strength - then approve.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: accept as-is, or request a specific refinement before confirming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>- PEOPLE / HR -</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Key person 1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Elena Vasquez, Co-Founder and CEO, 16 years in enterprise software, prior VP of Product at a public SaaS company, earns $650,000 a year in total cash compensation.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Full detail: name, title, years, background, wage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Key person 2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Rajan Mehta, Co-Founder and CTO, 15 years in distributed systems - let the consultant estimate his compensation.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Wage can be omitted - the app estimates it (wage_source shows it was estimated, not client-set).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Done adding people</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>After the two co-founders, say the key people list is complete.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>When to stop - triggers the people wrap-up (paragraphs + suggested future roles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Suggested roles - wage</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>If a VP of Sales or similar executive role is suggested, set its wage to $300,000.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: override a suggested role's estimated wage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Suggested roles - timing</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Any suggested additional executive hire should be planned for about 3 months out.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Behavior: set months-until-hire on a suggested role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: baselines (accept / adjust behaviors) -</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Revenue baseline</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Accept the Year-1 revenue baseline as presented.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Or: adjust a driver ('actually make PT utilization 75%'), or pick a presented option by number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Set COGS at about 24% of revenue - hosting, infrastructure, support, and services delivery.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Options: accept baseline / set a dollar amount / set a percent of revenue / 'use 0 for COGS'. Accept-then-adjust exercises the correction path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>The People-derived baseline will be far too low for our size - set Year-1 payroll to about $52 million; we run around 380 employees. Confirm when it's restated.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Accept, or push to an exact number. Baseline derives from the People section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>We spend about $34 million a year on sales and marketing.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phrasing tests the monthly-to-annual conversion (3k/mo should land as 36,000/yr). Or give an annual total or a percent of revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: the scalar questions (one each) -</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Monthly rent</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Office rent on our Bellevue headquarters is about $220,000 a month.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Or 'we work from home' - lands as 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Future rent expected</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Yes - we'll continue to need office space.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no boolean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Owner compensation</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>As CEO I take about $650,000 a year in cash compensation.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phrasing tests the x12 annualization (should land ~108,000). Or state an annual figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Other operating expense</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Other operating costs - software tools, travel, professional services, insurance - run about $900,000 a month.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Utilities, software, insurance, etc. - monthly figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Employee count</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>We have about 380 employees on payroll.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Whole number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>We spent about $4,000,000 recently on data-center hardware and office build-out.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Larger one-time purchases; 'none' lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Initial assets</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Capitalized equipment, servers, and build-out are worth about $18,000,000.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Total value of existing equipment/fixtures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Initial lease</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Beyond the office rent, we lease data-center and network equipment at about $60,000 a month.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Monthly lease beyond main rent; 'none' lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Initial equity</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>About $85,000,000 of equity has been raised into the business to date.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Owner/investor money invested to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>We carry about $40,000,000 in venture debt and a term loan.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANT: a value of 0 auto-fills the next three debt answers as 0 and skips those questions. Non-zero makes them all fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Other monthly debt payments</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>The debt service runs about $930,000 a month.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Annual interest</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Annual interest is about $3,200,000.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Annual principal</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>We pay down about $8,000,000 of principal a year.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Only asked when total debt is non-zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Cash on hand</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>About $30,000,000 in the bank.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Business cash balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise customers owe us about $14,000,000 on net-30 and net-60 terms.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Shorthand like '40k' is understood (lands 40,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>We owe about $6,000,000 to vendors and infrastructure providers.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Unpaid supplier invoices, utilities, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>None - we're a software business, no inventory.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>'None/zero' phrasing lands 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>- FINANCIALS: strategy + funding (end of intake) -</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Cash strategy</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Preserve cash - we're reinvesting into growth and extending our runway, no distributions.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Options: preserve cash / shareholder return / balanced. Answering vaguely on purpose tests the app's clarify-then-forced-choice ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Funding preference</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Fund it with a mix of both debt and equity.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>debt / equity / both. Choosing debt-only or equity-only SKIPS the split question; 'both' triggers it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Funding split</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Roughly thirty percent debt and seventy percent equity - mostly venture equity with some venture debt.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Only asked after 'both'. Words work ('seventy percent debt'); lands as 0.7 / 0.5 / 0.3 debt share - off-menu answers snap to the nearest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>- CROSS-CUTTING CONVERSATION BEHAVIORS -</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Ask a question back</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>When milestones come up, first ask the consultant what counts as a milestone before giving your answer.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Tests the answer-a-question-read-only path (should not corrupt any captured data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Compound answer</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>When asked about delivery, answer that and also volunteer the sales channel in the same reply.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Tests multi-fact extraction from one message.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>